--- a/Budget.xlsx
+++ b/Budget.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1059706fb0152c6d/Desktop/BUDGET/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1059706fb0152c6d/Desktop/BUDGET/Dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2016" documentId="8_{09355C44-89CB-488A-BB21-8DE5232B736C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EB827A-61FF-4816-AFDA-50BDD8F84531}"/>
+  <xr:revisionPtr revIDLastSave="2027" documentId="8_{09355C44-89CB-488A-BB21-8DE5232B736C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956BCDB2-0E1C-46AE-BF57-8A2BD453DA14}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{6A122ACA-E9AC-4C58-B0E2-DFCC91437B7B}"/>
   </bookViews>
@@ -697,7 +697,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1413,7 +1413,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1474,7 +1474,6 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1488,13 +1487,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1526,6 +1522,81 @@
     <cellStyle name="Table Amount" xfId="4" xr:uid="{27BC3548-E818-40AB-A24E-1112E6BB55F5}"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1646,37 +1717,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1708,50 +1748,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3527,6 +3523,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9EEDE2C-EDEE-4D12-91C5-2AC67DE2783D}" name="Table2" displayName="Table2" ref="A1:I696" totalsRowShown="0">
   <autoFilter ref="A1:I696" xr:uid="{A9EEDE2C-EDEE-4D12-91C5-2AC67DE2783D}"/>
@@ -3534,14 +3534,14 @@
     <sortCondition ref="B2:B696"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3B5E47AD-ED2A-4CB6-85BE-575154507E16}" name="month" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{3B5E47AD-ED2A-4CB6-85BE-575154507E16}" name="month" dataDxfId="20">
       <calculatedColumnFormula>TEXT(Table2[[#This Row],[date]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{146AE3DA-A46C-4C74-AAA4-01958C053366}" name="date" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{146AE3DA-A46C-4C74-AAA4-01958C053366}" name="date" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{4474B80D-CEC8-4DF1-ABCA-8F9617FB3A2A}" name="decription "/>
     <tableColumn id="4" xr3:uid="{C4BA36E6-CD32-42C3-900B-47C445374042}" name="category"/>
-    <tableColumn id="5" xr3:uid="{688A08D0-624C-4193-8708-B515E2D72427}" name="income" dataDxfId="12" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{A4269F05-E5E9-47C3-8257-258F52F9EF70}" name="debit" dataDxfId="11" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{688A08D0-624C-4193-8708-B515E2D72427}" name="income" dataDxfId="18" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{A4269F05-E5E9-47C3-8257-258F52F9EF70}" name="debit" dataDxfId="17" dataCellStyle="Currency"/>
     <tableColumn id="7" xr3:uid="{4B0A68F5-3CDF-4287-9967-F8A2CC90FA24}" name="balance" dataCellStyle="Currency"/>
     <tableColumn id="8" xr3:uid="{5CCF96CD-35DD-4238-BF1A-67259A9D403A}" name="CREDIT"/>
     <tableColumn id="9" xr3:uid="{398CA709-62CE-4B1D-A54C-F0F30EEC3B8B}" name="Notes"/>
@@ -3551,23 +3551,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{597FEBA0-E60E-4A3D-A030-A40D30B111F5}" name="Table1" displayName="Table1" ref="A1:E18" totalsRowShown="0" headerRowDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{597FEBA0-E60E-4A3D-A030-A40D30B111F5}" name="Table1" displayName="Table1" ref="A1:E18" totalsRowShown="0" headerRowDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:E18" xr:uid="{597FEBA0-E60E-4A3D-A030-A40D30B111F5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E3B108B1-2BC0-4C9F-BC48-C8154A3774A3}" name="Where?" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{01A080BA-5798-4A20-AA6C-70C3CB7B46D2}" name="When?" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5A6E8153-D5BE-49FD-B27D-DB445DF7032F}" name="What?" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{AC4C3AC1-06C6-4C56-AE67-54A7CC35BCD9}" name="Details" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{B5120C69-C136-46ED-A25B-C4FC373CC7A5}" name="Who" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E3B108B1-2BC0-4C9F-BC48-C8154A3774A3}" name="Where?" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{01A080BA-5798-4A20-AA6C-70C3CB7B46D2}" name="When?" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{5A6E8153-D5BE-49FD-B27D-DB445DF7032F}" name="What?" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{AC4C3AC1-06C6-4C56-AE67-54A7CC35BCD9}" name="Details" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{B5120C69-C136-46ED-A25B-C4FC373CC7A5}" name="Who" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3605,7 +3605,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3711,7 +3711,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3853,7 +3853,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3865,7 +3865,7 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:M699"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -3885,7 +3885,7 @@
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M2" s="22"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4027,7 +4027,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4064,7 +4064,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4101,7 +4101,7 @@
         <v>0.28000000000020009</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4138,7 +4138,7 @@
         <v>92.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4175,7 +4175,7 @@
         <v>338.09000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4212,7 +4212,7 @@
         <v>418.54</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4249,7 +4249,7 @@
         <v>167.29999999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4286,7 +4286,7 @@
         <v>-153.99</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4323,7 +4323,7 @@
         <v>53.930000000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4360,7 +4360,7 @@
         <v>-223.43999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4397,7 +4397,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4526,7 +4526,7 @@
       <c r="L18" s="28"/>
       <c r="M18" s="24"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4559,7 +4559,7 @@
       <c r="L19" s="28"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4600,7 +4600,7 @@
         <v>3481.96</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4623,7 +4623,7 @@
         <v>1653.4500000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4646,7 +4646,7 @@
         <v>1039.4500000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4671,7 +4671,7 @@
       <c r="K23" s="31"/>
       <c r="M23" s="32"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4694,7 +4694,7 @@
         <v>891.96000000000072</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4717,7 +4717,7 @@
         <v>881.19000000000074</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4740,7 +4740,7 @@
         <v>850.65000000000077</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4763,7 +4763,7 @@
         <v>839.65000000000077</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4786,7 +4786,7 @@
         <v>772.65000000000077</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4809,7 +4809,7 @@
         <v>750.64000000000078</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4832,7 +4832,7 @@
         <v>736.34000000000083</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4855,7 +4855,7 @@
         <v>681.71000000000083</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4878,7 +4878,7 @@
         <v>649.01000000000079</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4901,7 +4901,7 @@
         <v>637.96000000000083</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4924,7 +4924,7 @@
         <v>536.6200000000008</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4947,7 +4947,7 @@
         <v>503.08000000000078</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4970,7 +4970,7 @@
         <v>459.0000000000008</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -4993,7 +4993,7 @@
         <v>384.9300000000008</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5016,7 +5016,7 @@
         <v>304.83000000000084</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5039,7 +5039,7 @@
         <v>301.09000000000083</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5062,7 +5062,7 @@
         <v>262.23000000000081</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5085,7 +5085,7 @@
         <v>251.23000000000081</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5108,7 +5108,7 @@
         <v>128.1800000000008</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5131,7 +5131,7 @@
         <v>78.180000000000803</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5154,7 +5154,7 @@
         <v>2111.7100000000009</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5177,7 +5177,7 @@
         <v>4022.9800000000009</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5200,7 +5200,7 @@
         <v>4003.0400000000009</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5223,7 +5223,7 @@
         <v>3997.0500000000011</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5246,7 +5246,7 @@
         <v>3983.900000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5269,7 +5269,7 @@
         <v>3944.5700000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5292,7 +5292,7 @@
         <v>3927.1000000000013</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5315,7 +5315,7 @@
         <v>3901.0400000000013</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5342,7 +5342,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5365,7 +5365,7 @@
         <v>3878.3300000000013</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5388,7 +5388,7 @@
         <v>3863.0500000000011</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5411,7 +5411,7 @@
         <v>3849.940000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5434,7 +5434,7 @@
         <v>3845.2300000000009</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5457,7 +5457,7 @@
         <v>3820.9900000000011</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5480,7 +5480,7 @@
         <v>3770.9900000000011</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5503,7 +5503,7 @@
         <v>3733.5700000000011</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5526,7 +5526,7 @@
         <v>3689.650000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5549,7 +5549,7 @@
         <v>3634.630000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5572,7 +5572,7 @@
         <v>3547.9900000000011</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5595,7 +5595,7 @@
         <v>3540.2500000000014</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5618,7 +5618,7 @@
         <v>3521.3900000000012</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5641,7 +5641,7 @@
         <v>3504.1000000000013</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5664,7 +5664,7 @@
         <v>3494.1100000000015</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5687,7 +5687,7 @@
         <v>3472.0800000000013</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5710,7 +5710,7 @@
         <v>3460.7000000000012</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5733,7 +5733,7 @@
         <v>3434.440000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5756,7 +5756,7 @@
         <v>3414.440000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5782,7 +5782,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5805,7 +5805,7 @@
         <v>3307.7100000000009</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5828,7 +5828,7 @@
         <v>3265.0400000000009</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5851,7 +5851,7 @@
         <v>3235.4500000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5874,7 +5874,7 @@
         <v>3209.9600000000009</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5897,7 +5897,7 @@
         <v>3200.1200000000008</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="L77" s="9"/>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5944,7 +5944,7 @@
         <v>3137.3300000000008</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5967,7 +5967,7 @@
         <v>3133.5700000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -5990,7 +5990,7 @@
         <v>3130.0500000000006</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6013,7 +6013,7 @@
         <v>3100.4800000000005</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6036,7 +6036,7 @@
         <v>2986.5500000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6059,7 +6059,7 @@
         <v>2886.5500000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6082,7 +6082,7 @@
         <v>2827.4200000000005</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6105,7 +6105,7 @@
         <v>2815.2200000000007</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6128,7 +6128,7 @@
         <v>2805.1900000000005</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6151,7 +6151,7 @@
         <v>2774.6500000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6174,7 +6174,7 @@
         <v>2710.0500000000006</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6197,7 +6197,7 @@
         <v>4812.2000000000007</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6223,7 +6223,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6246,7 +6246,7 @@
         <v>9913.2800000000007</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6269,7 +6269,7 @@
         <v>11946.810000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6292,7 +6292,7 @@
         <v>13858.070000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6315,7 +6315,7 @@
         <v>13819.53</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6338,7 +6338,7 @@
         <v>13759.070000000002</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6361,7 +6361,7 @@
         <v>13648.090000000002</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6384,7 +6384,7 @@
         <v>13631.650000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6407,7 +6407,7 @@
         <v>13630.160000000002</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6430,7 +6430,7 @@
         <v>13572.430000000002</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6453,7 +6453,7 @@
         <v>13572.640000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6476,7 +6476,7 @@
         <v>13759.800000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6499,7 +6499,7 @@
         <v>13650.340000000002</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -6522,7 +6522,7 @@
         <v>11550.340000000002</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6545,7 +6545,7 @@
         <v>10758.340000000002</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6568,7 +6568,7 @@
         <v>10500.340000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6591,7 +6591,7 @@
         <v>7764.6200000000026</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6614,7 +6614,7 @@
         <v>1764.6200000000026</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6637,7 +6637,7 @@
         <v>1664.6200000000026</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6660,7 +6660,7 @@
         <v>1604.2100000000025</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6683,7 +6683,7 @@
         <v>1551.6300000000026</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6706,7 +6706,7 @@
         <v>1506.8400000000026</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6714,10 +6714,10 @@
       <c r="B112" s="3">
         <v>46054</v>
       </c>
-      <c r="C112" s="60" t="s">
+      <c r="C112" t="s">
         <v>107</v>
       </c>
-      <c r="D112" s="60" t="s">
+      <c r="D112" t="s">
         <v>36</v>
       </c>
       <c r="E112" s="33"/>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6753,7 +6753,7 @@
         <v>1457.8300000000027</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6776,7 +6776,7 @@
         <v>1442.5800000000027</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6799,7 +6799,7 @@
         <v>1432.5600000000027</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6822,7 +6822,7 @@
         <v>1411.9000000000026</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="I117" s="30"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6872,7 +6872,7 @@
         <v>1288.8600000000026</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6895,7 +6895,7 @@
         <v>1269.7100000000025</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6918,7 +6918,7 @@
         <v>1219.7100000000025</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6941,7 +6941,7 @@
         <v>1185.5200000000025</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6964,7 +6964,7 @@
         <v>1181.7600000000025</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -6987,7 +6987,7 @@
         <v>1156.6400000000026</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7010,7 +7010,7 @@
         <v>624.73000000000263</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7033,7 +7033,7 @@
         <v>582.72000000000264</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7056,7 +7056,7 @@
         <v>582.5200000000026</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7079,7 +7079,7 @@
         <v>572.58000000000254</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7102,7 +7102,7 @@
         <v>499.81000000000256</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7125,7 +7125,7 @@
         <v>473.58000000000254</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7148,7 +7148,7 @@
         <v>430.24000000000251</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7171,7 +7171,7 @@
         <v>405.16000000000253</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7194,7 +7194,7 @@
         <v>330.16000000000253</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7217,7 +7217,7 @@
         <v>230.50000000000253</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7240,7 +7240,7 @@
         <v>171.23000000000252</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7263,7 +7263,7 @@
         <v>157.85000000000252</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7286,7 +7286,7 @@
         <v>154.09000000000253</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7309,7 +7309,7 @@
         <v>104.92000000000253</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7332,7 +7332,7 @@
         <v>97.870000000002534</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7355,7 +7355,7 @@
         <v>53.790000000002536</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7378,7 +7378,7 @@
         <v>2086.7900000000027</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7401,7 +7401,7 @@
         <v>2083.0300000000025</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7424,7 +7424,7 @@
         <v>2077.6200000000026</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7447,7 +7447,7 @@
         <v>1916.8100000000027</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7470,7 +7470,7 @@
         <v>1793.7600000000027</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7493,7 +7493,7 @@
         <v>1748.5500000000027</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7516,7 +7516,7 @@
         <v>1695.8200000000027</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7539,7 +7539,7 @@
         <v>1679.9200000000026</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7565,7 +7565,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="K149" s="9"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7612,7 +7612,7 @@
         <v>3539.2000000000025</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7635,7 +7635,7 @@
         <v>3532.4300000000026</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7658,7 +7658,7 @@
         <v>3520.8800000000024</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7681,7 +7681,7 @@
         <v>3439.4200000000023</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7707,7 +7707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7730,7 +7730,7 @@
         <v>3330.7800000000025</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7753,7 +7753,7 @@
         <v>3323.8300000000027</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7776,7 +7776,7 @@
         <v>3303.7100000000028</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7799,7 +7799,7 @@
         <v>3221.9200000000028</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7822,7 +7822,7 @@
         <v>3194.6600000000026</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7845,7 +7845,7 @@
         <v>3093.8800000000024</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7868,7 +7868,7 @@
         <v>3074.9700000000025</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7891,7 +7891,7 @@
         <v>3028.3900000000026</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7914,7 +7914,7 @@
         <v>2929.6400000000026</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7937,7 +7937,7 @@
         <v>2666.6400000000026</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7961,7 +7961,7 @@
         <v>32.71</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -7987,7 +7987,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8010,7 +8010,7 @@
         <v>2761.0000000000027</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8036,7 +8036,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8059,7 +8059,7 @@
         <v>2773.0400000000027</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8082,7 +8082,7 @@
         <v>2730.0600000000027</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8105,7 +8105,7 @@
         <v>2721.4400000000028</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8128,7 +8128,7 @@
         <v>2718.8900000000026</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8151,7 +8151,7 @@
         <v>2713.1600000000026</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8174,7 +8174,7 @@
         <v>2641.8800000000024</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8197,7 +8197,7 @@
         <v>2638.6800000000026</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>February</v>
@@ -8220,7 +8220,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8230,7 +8230,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8240,7 +8240,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8250,7 +8250,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8260,7 +8260,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8270,7 +8270,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8280,7 +8280,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8290,7 +8290,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8300,7 +8300,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8310,7 +8310,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8320,7 +8320,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8330,7 +8330,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8340,7 +8340,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8350,7 +8350,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8360,7 +8360,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8370,7 +8370,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8380,7 +8380,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8390,7 +8390,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8400,7 +8400,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8410,7 +8410,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8420,7 +8420,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8430,7 +8430,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8440,7 +8440,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="J199" s="30"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="J200" s="30"/>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="J201" s="30"/>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="J202" s="30"/>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8494,7 +8494,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8504,7 +8504,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8514,7 +8514,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8524,7 +8524,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8534,7 +8534,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8544,7 +8544,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8554,7 +8554,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8564,7 +8564,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8574,7 +8574,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8584,7 +8584,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8594,7 +8594,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8604,7 +8604,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8614,7 +8614,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8624,7 +8624,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8634,7 +8634,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8644,7 +8644,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8654,7 +8654,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8664,7 +8664,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8674,7 +8674,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8684,7 +8684,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8694,7 +8694,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8704,7 +8704,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8714,7 +8714,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8724,7 +8724,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8734,7 +8734,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8744,7 +8744,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8754,7 +8754,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8764,7 +8764,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="K231" s="9"/>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8785,7 +8785,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8795,7 +8795,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8805,7 +8805,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8815,7 +8815,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8825,7 +8825,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8835,7 +8835,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8845,7 +8845,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8855,7 +8855,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8865,7 +8865,7 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="str">
         <f>TEXT(Table2[[#This Row],[date]],"MMMM")</f>
         <v>January</v>
@@ -8875,480 +8875,480 @@
         <v>2616.5700000000024</v>
       </c>
     </row>
-    <row r="242" spans="1:7"/>
-    <row r="243" spans="1:7"/>
-    <row r="244" spans="1:7"/>
-    <row r="245" spans="1:7"/>
-    <row r="246" spans="1:7"/>
-    <row r="247" spans="1:7"/>
-    <row r="248" spans="1:7"/>
-    <row r="249" spans="1:7"/>
-    <row r="250" spans="1:7"/>
-    <row r="251" spans="1:7"/>
-    <row r="252" spans="1:7"/>
-    <row r="253" spans="1:7"/>
-    <row r="254" spans="1:7"/>
-    <row r="255" spans="1:7"/>
-    <row r="256" spans="1:7"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="257" x14ac:dyDescent="0.25"/>
+    <row r="258" x14ac:dyDescent="0.25"/>
+    <row r="259" x14ac:dyDescent="0.25"/>
+    <row r="260" x14ac:dyDescent="0.25"/>
+    <row r="261" x14ac:dyDescent="0.25"/>
+    <row r="262" x14ac:dyDescent="0.25"/>
+    <row r="263" x14ac:dyDescent="0.25"/>
+    <row r="264" x14ac:dyDescent="0.25"/>
+    <row r="265" x14ac:dyDescent="0.25"/>
+    <row r="266" x14ac:dyDescent="0.25"/>
+    <row r="267" x14ac:dyDescent="0.25"/>
+    <row r="268" x14ac:dyDescent="0.25"/>
+    <row r="269" x14ac:dyDescent="0.25"/>
+    <row r="270" x14ac:dyDescent="0.25"/>
+    <row r="271" x14ac:dyDescent="0.25"/>
+    <row r="272" x14ac:dyDescent="0.25"/>
+    <row r="273" x14ac:dyDescent="0.25"/>
+    <row r="274" x14ac:dyDescent="0.25"/>
+    <row r="275" x14ac:dyDescent="0.25"/>
+    <row r="276" x14ac:dyDescent="0.25"/>
+    <row r="277" x14ac:dyDescent="0.25"/>
+    <row r="278" x14ac:dyDescent="0.25"/>
+    <row r="279" x14ac:dyDescent="0.25"/>
+    <row r="280" x14ac:dyDescent="0.25"/>
+    <row r="281" x14ac:dyDescent="0.25"/>
+    <row r="282" x14ac:dyDescent="0.25"/>
+    <row r="283" x14ac:dyDescent="0.25"/>
+    <row r="284" x14ac:dyDescent="0.25"/>
+    <row r="285" x14ac:dyDescent="0.25"/>
+    <row r="286" x14ac:dyDescent="0.25"/>
+    <row r="287" x14ac:dyDescent="0.25"/>
+    <row r="288" x14ac:dyDescent="0.25"/>
+    <row r="289" x14ac:dyDescent="0.25"/>
+    <row r="290" x14ac:dyDescent="0.25"/>
+    <row r="291" x14ac:dyDescent="0.25"/>
+    <row r="292" x14ac:dyDescent="0.25"/>
+    <row r="293" x14ac:dyDescent="0.25"/>
+    <row r="294" x14ac:dyDescent="0.25"/>
+    <row r="295" x14ac:dyDescent="0.25"/>
+    <row r="296" x14ac:dyDescent="0.25"/>
+    <row r="297" x14ac:dyDescent="0.25"/>
+    <row r="298" x14ac:dyDescent="0.25"/>
+    <row r="299" x14ac:dyDescent="0.25"/>
+    <row r="300" x14ac:dyDescent="0.25"/>
+    <row r="301" x14ac:dyDescent="0.25"/>
+    <row r="302" x14ac:dyDescent="0.25"/>
+    <row r="303" x14ac:dyDescent="0.25"/>
+    <row r="304" x14ac:dyDescent="0.25"/>
+    <row r="305" x14ac:dyDescent="0.25"/>
+    <row r="306" x14ac:dyDescent="0.25"/>
+    <row r="307" x14ac:dyDescent="0.25"/>
+    <row r="308" x14ac:dyDescent="0.25"/>
+    <row r="309" x14ac:dyDescent="0.25"/>
+    <row r="310" x14ac:dyDescent="0.25"/>
+    <row r="311" x14ac:dyDescent="0.25"/>
+    <row r="312" x14ac:dyDescent="0.25"/>
+    <row r="313" x14ac:dyDescent="0.25"/>
+    <row r="314" x14ac:dyDescent="0.25"/>
+    <row r="315" x14ac:dyDescent="0.25"/>
+    <row r="316" x14ac:dyDescent="0.25"/>
+    <row r="317" x14ac:dyDescent="0.25"/>
+    <row r="318" x14ac:dyDescent="0.25"/>
+    <row r="319" x14ac:dyDescent="0.25"/>
+    <row r="320" x14ac:dyDescent="0.25"/>
+    <row r="321" x14ac:dyDescent="0.25"/>
+    <row r="322" x14ac:dyDescent="0.25"/>
+    <row r="323" x14ac:dyDescent="0.25"/>
+    <row r="324" x14ac:dyDescent="0.25"/>
+    <row r="325" x14ac:dyDescent="0.25"/>
+    <row r="326" x14ac:dyDescent="0.25"/>
+    <row r="327" x14ac:dyDescent="0.25"/>
+    <row r="328" x14ac:dyDescent="0.25"/>
+    <row r="329" x14ac:dyDescent="0.25"/>
+    <row r="330" x14ac:dyDescent="0.25"/>
+    <row r="331" x14ac:dyDescent="0.25"/>
+    <row r="332" x14ac:dyDescent="0.25"/>
+    <row r="333" x14ac:dyDescent="0.25"/>
+    <row r="334" x14ac:dyDescent="0.25"/>
+    <row r="335" x14ac:dyDescent="0.25"/>
+    <row r="336" x14ac:dyDescent="0.25"/>
+    <row r="337" x14ac:dyDescent="0.25"/>
+    <row r="338" x14ac:dyDescent="0.25"/>
+    <row r="339" x14ac:dyDescent="0.25"/>
+    <row r="340" x14ac:dyDescent="0.25"/>
+    <row r="341" x14ac:dyDescent="0.25"/>
+    <row r="342" x14ac:dyDescent="0.25"/>
+    <row r="343" x14ac:dyDescent="0.25"/>
+    <row r="344" x14ac:dyDescent="0.25"/>
+    <row r="345" x14ac:dyDescent="0.25"/>
+    <row r="346" x14ac:dyDescent="0.25"/>
+    <row r="347" x14ac:dyDescent="0.25"/>
+    <row r="348" x14ac:dyDescent="0.25"/>
+    <row r="349" x14ac:dyDescent="0.25"/>
+    <row r="350" x14ac:dyDescent="0.25"/>
+    <row r="351" x14ac:dyDescent="0.25"/>
+    <row r="352" x14ac:dyDescent="0.25"/>
+    <row r="353" x14ac:dyDescent="0.25"/>
+    <row r="354" x14ac:dyDescent="0.25"/>
+    <row r="355" x14ac:dyDescent="0.25"/>
+    <row r="356" x14ac:dyDescent="0.25"/>
+    <row r="357" x14ac:dyDescent="0.25"/>
+    <row r="358" x14ac:dyDescent="0.25"/>
+    <row r="359" x14ac:dyDescent="0.25"/>
+    <row r="360" x14ac:dyDescent="0.25"/>
+    <row r="361" x14ac:dyDescent="0.25"/>
+    <row r="362" x14ac:dyDescent="0.25"/>
+    <row r="363" x14ac:dyDescent="0.25"/>
+    <row r="364" x14ac:dyDescent="0.25"/>
+    <row r="365" x14ac:dyDescent="0.25"/>
+    <row r="366" x14ac:dyDescent="0.25"/>
+    <row r="367" x14ac:dyDescent="0.25"/>
+    <row r="368" x14ac:dyDescent="0.25"/>
+    <row r="369" x14ac:dyDescent="0.25"/>
+    <row r="370" x14ac:dyDescent="0.25"/>
+    <row r="371" x14ac:dyDescent="0.25"/>
+    <row r="372" x14ac:dyDescent="0.25"/>
+    <row r="373" x14ac:dyDescent="0.25"/>
+    <row r="374" x14ac:dyDescent="0.25"/>
+    <row r="375" x14ac:dyDescent="0.25"/>
+    <row r="376" x14ac:dyDescent="0.25"/>
+    <row r="377" x14ac:dyDescent="0.25"/>
+    <row r="378" x14ac:dyDescent="0.25"/>
+    <row r="379" x14ac:dyDescent="0.25"/>
+    <row r="380" x14ac:dyDescent="0.25"/>
+    <row r="381" x14ac:dyDescent="0.25"/>
+    <row r="382" x14ac:dyDescent="0.25"/>
+    <row r="383" x14ac:dyDescent="0.25"/>
+    <row r="384" x14ac:dyDescent="0.25"/>
+    <row r="385" x14ac:dyDescent="0.25"/>
+    <row r="386" x14ac:dyDescent="0.25"/>
+    <row r="387" x14ac:dyDescent="0.25"/>
+    <row r="388" x14ac:dyDescent="0.25"/>
+    <row r="389" x14ac:dyDescent="0.25"/>
+    <row r="390" x14ac:dyDescent="0.25"/>
+    <row r="391" x14ac:dyDescent="0.25"/>
+    <row r="392" x14ac:dyDescent="0.25"/>
+    <row r="393" x14ac:dyDescent="0.25"/>
+    <row r="394" x14ac:dyDescent="0.25"/>
+    <row r="395" x14ac:dyDescent="0.25"/>
+    <row r="396" x14ac:dyDescent="0.25"/>
+    <row r="397" x14ac:dyDescent="0.25"/>
+    <row r="398" x14ac:dyDescent="0.25"/>
+    <row r="399" x14ac:dyDescent="0.25"/>
+    <row r="400" x14ac:dyDescent="0.25"/>
+    <row r="401" x14ac:dyDescent="0.25"/>
+    <row r="402" x14ac:dyDescent="0.25"/>
+    <row r="403" x14ac:dyDescent="0.25"/>
+    <row r="404" x14ac:dyDescent="0.25"/>
+    <row r="405" x14ac:dyDescent="0.25"/>
+    <row r="406" x14ac:dyDescent="0.25"/>
+    <row r="407" x14ac:dyDescent="0.25"/>
+    <row r="408" x14ac:dyDescent="0.25"/>
+    <row r="409" x14ac:dyDescent="0.25"/>
+    <row r="410" x14ac:dyDescent="0.25"/>
+    <row r="411" x14ac:dyDescent="0.25"/>
+    <row r="412" x14ac:dyDescent="0.25"/>
+    <row r="413" x14ac:dyDescent="0.25"/>
+    <row r="414" x14ac:dyDescent="0.25"/>
+    <row r="415" x14ac:dyDescent="0.25"/>
+    <row r="416" x14ac:dyDescent="0.25"/>
+    <row r="417" x14ac:dyDescent="0.25"/>
+    <row r="418" x14ac:dyDescent="0.25"/>
+    <row r="419" x14ac:dyDescent="0.25"/>
+    <row r="420" x14ac:dyDescent="0.25"/>
+    <row r="421" x14ac:dyDescent="0.25"/>
+    <row r="422" x14ac:dyDescent="0.25"/>
+    <row r="423" x14ac:dyDescent="0.25"/>
+    <row r="424" x14ac:dyDescent="0.25"/>
+    <row r="425" x14ac:dyDescent="0.25"/>
+    <row r="426" x14ac:dyDescent="0.25"/>
+    <row r="427" x14ac:dyDescent="0.25"/>
+    <row r="428" x14ac:dyDescent="0.25"/>
+    <row r="429" x14ac:dyDescent="0.25"/>
+    <row r="430" x14ac:dyDescent="0.25"/>
+    <row r="431" x14ac:dyDescent="0.25"/>
+    <row r="432" x14ac:dyDescent="0.25"/>
+    <row r="433" x14ac:dyDescent="0.25"/>
+    <row r="434" x14ac:dyDescent="0.25"/>
+    <row r="435" x14ac:dyDescent="0.25"/>
+    <row r="436" x14ac:dyDescent="0.25"/>
+    <row r="437" x14ac:dyDescent="0.25"/>
+    <row r="438" x14ac:dyDescent="0.25"/>
+    <row r="439" x14ac:dyDescent="0.25"/>
+    <row r="440" x14ac:dyDescent="0.25"/>
+    <row r="441" x14ac:dyDescent="0.25"/>
+    <row r="442" x14ac:dyDescent="0.25"/>
+    <row r="443" x14ac:dyDescent="0.25"/>
+    <row r="444" x14ac:dyDescent="0.25"/>
+    <row r="445" x14ac:dyDescent="0.25"/>
+    <row r="446" x14ac:dyDescent="0.25"/>
+    <row r="447" x14ac:dyDescent="0.25"/>
+    <row r="448" x14ac:dyDescent="0.25"/>
+    <row r="449" x14ac:dyDescent="0.25"/>
+    <row r="450" x14ac:dyDescent="0.25"/>
+    <row r="451" x14ac:dyDescent="0.25"/>
+    <row r="452" x14ac:dyDescent="0.25"/>
+    <row r="453" x14ac:dyDescent="0.25"/>
+    <row r="454" x14ac:dyDescent="0.25"/>
+    <row r="455" x14ac:dyDescent="0.25"/>
+    <row r="456" x14ac:dyDescent="0.25"/>
+    <row r="457" x14ac:dyDescent="0.25"/>
+    <row r="458" x14ac:dyDescent="0.25"/>
+    <row r="459" x14ac:dyDescent="0.25"/>
+    <row r="460" x14ac:dyDescent="0.25"/>
+    <row r="461" x14ac:dyDescent="0.25"/>
+    <row r="462" x14ac:dyDescent="0.25"/>
+    <row r="463" x14ac:dyDescent="0.25"/>
+    <row r="464" x14ac:dyDescent="0.25"/>
+    <row r="465" x14ac:dyDescent="0.25"/>
+    <row r="466" x14ac:dyDescent="0.25"/>
+    <row r="467" x14ac:dyDescent="0.25"/>
+    <row r="468" x14ac:dyDescent="0.25"/>
+    <row r="469" x14ac:dyDescent="0.25"/>
+    <row r="470" x14ac:dyDescent="0.25"/>
+    <row r="471" x14ac:dyDescent="0.25"/>
+    <row r="472" x14ac:dyDescent="0.25"/>
+    <row r="473" x14ac:dyDescent="0.25"/>
+    <row r="474" x14ac:dyDescent="0.25"/>
+    <row r="475" x14ac:dyDescent="0.25"/>
+    <row r="476" x14ac:dyDescent="0.25"/>
+    <row r="477" x14ac:dyDescent="0.25"/>
+    <row r="478" x14ac:dyDescent="0.25"/>
+    <row r="479" x14ac:dyDescent="0.25"/>
+    <row r="480" x14ac:dyDescent="0.25"/>
+    <row r="481" x14ac:dyDescent="0.25"/>
+    <row r="482" x14ac:dyDescent="0.25"/>
+    <row r="483" x14ac:dyDescent="0.25"/>
+    <row r="484" x14ac:dyDescent="0.25"/>
+    <row r="485" x14ac:dyDescent="0.25"/>
+    <row r="486" x14ac:dyDescent="0.25"/>
+    <row r="487" x14ac:dyDescent="0.25"/>
+    <row r="488" x14ac:dyDescent="0.25"/>
+    <row r="489" x14ac:dyDescent="0.25"/>
+    <row r="490" x14ac:dyDescent="0.25"/>
+    <row r="491" x14ac:dyDescent="0.25"/>
+    <row r="492" x14ac:dyDescent="0.25"/>
+    <row r="493" x14ac:dyDescent="0.25"/>
+    <row r="494" x14ac:dyDescent="0.25"/>
+    <row r="495" x14ac:dyDescent="0.25"/>
+    <row r="496" x14ac:dyDescent="0.25"/>
+    <row r="497" x14ac:dyDescent="0.25"/>
+    <row r="498" x14ac:dyDescent="0.25"/>
+    <row r="499" x14ac:dyDescent="0.25"/>
+    <row r="500" x14ac:dyDescent="0.25"/>
+    <row r="501" x14ac:dyDescent="0.25"/>
+    <row r="502" x14ac:dyDescent="0.25"/>
+    <row r="503" x14ac:dyDescent="0.25"/>
+    <row r="504" x14ac:dyDescent="0.25"/>
+    <row r="505" x14ac:dyDescent="0.25"/>
+    <row r="506" x14ac:dyDescent="0.25"/>
+    <row r="507" x14ac:dyDescent="0.25"/>
+    <row r="508" x14ac:dyDescent="0.25"/>
+    <row r="509" x14ac:dyDescent="0.25"/>
+    <row r="510" x14ac:dyDescent="0.25"/>
+    <row r="511" x14ac:dyDescent="0.25"/>
+    <row r="512" x14ac:dyDescent="0.25"/>
+    <row r="513" x14ac:dyDescent="0.25"/>
+    <row r="514" x14ac:dyDescent="0.25"/>
+    <row r="515" x14ac:dyDescent="0.25"/>
+    <row r="516" x14ac:dyDescent="0.25"/>
+    <row r="517" x14ac:dyDescent="0.25"/>
+    <row r="518" x14ac:dyDescent="0.25"/>
+    <row r="519" x14ac:dyDescent="0.25"/>
+    <row r="520" x14ac:dyDescent="0.25"/>
+    <row r="521" x14ac:dyDescent="0.25"/>
+    <row r="522" x14ac:dyDescent="0.25"/>
+    <row r="523" x14ac:dyDescent="0.25"/>
+    <row r="524" x14ac:dyDescent="0.25"/>
+    <row r="525" x14ac:dyDescent="0.25"/>
+    <row r="526" x14ac:dyDescent="0.25"/>
+    <row r="527" x14ac:dyDescent="0.25"/>
+    <row r="528" x14ac:dyDescent="0.25"/>
+    <row r="529" x14ac:dyDescent="0.25"/>
+    <row r="530" x14ac:dyDescent="0.25"/>
+    <row r="531" x14ac:dyDescent="0.25"/>
+    <row r="532" x14ac:dyDescent="0.25"/>
+    <row r="533" x14ac:dyDescent="0.25"/>
+    <row r="534" x14ac:dyDescent="0.25"/>
+    <row r="535" x14ac:dyDescent="0.25"/>
+    <row r="536" x14ac:dyDescent="0.25"/>
+    <row r="537" x14ac:dyDescent="0.25"/>
+    <row r="538" x14ac:dyDescent="0.25"/>
+    <row r="539" x14ac:dyDescent="0.25"/>
+    <row r="540" x14ac:dyDescent="0.25"/>
+    <row r="541" x14ac:dyDescent="0.25"/>
+    <row r="542" x14ac:dyDescent="0.25"/>
+    <row r="543" x14ac:dyDescent="0.25"/>
+    <row r="544" x14ac:dyDescent="0.25"/>
+    <row r="545" x14ac:dyDescent="0.25"/>
+    <row r="546" x14ac:dyDescent="0.25"/>
+    <row r="547" x14ac:dyDescent="0.25"/>
+    <row r="548" x14ac:dyDescent="0.25"/>
+    <row r="549" x14ac:dyDescent="0.25"/>
+    <row r="550" x14ac:dyDescent="0.25"/>
+    <row r="551" x14ac:dyDescent="0.25"/>
+    <row r="552" x14ac:dyDescent="0.25"/>
+    <row r="553" x14ac:dyDescent="0.25"/>
+    <row r="554" x14ac:dyDescent="0.25"/>
+    <row r="555" x14ac:dyDescent="0.25"/>
+    <row r="556" x14ac:dyDescent="0.25"/>
+    <row r="557" x14ac:dyDescent="0.25"/>
+    <row r="558" x14ac:dyDescent="0.25"/>
+    <row r="559" x14ac:dyDescent="0.25"/>
+    <row r="560" x14ac:dyDescent="0.25"/>
+    <row r="561" x14ac:dyDescent="0.25"/>
+    <row r="562" x14ac:dyDescent="0.25"/>
+    <row r="563" x14ac:dyDescent="0.25"/>
+    <row r="564" x14ac:dyDescent="0.25"/>
+    <row r="565" x14ac:dyDescent="0.25"/>
+    <row r="566" x14ac:dyDescent="0.25"/>
+    <row r="567" x14ac:dyDescent="0.25"/>
+    <row r="568" x14ac:dyDescent="0.25"/>
+    <row r="569" x14ac:dyDescent="0.25"/>
+    <row r="570" x14ac:dyDescent="0.25"/>
+    <row r="571" x14ac:dyDescent="0.25"/>
+    <row r="572" x14ac:dyDescent="0.25"/>
+    <row r="573" x14ac:dyDescent="0.25"/>
+    <row r="574" x14ac:dyDescent="0.25"/>
+    <row r="575" x14ac:dyDescent="0.25"/>
+    <row r="576" x14ac:dyDescent="0.25"/>
+    <row r="577" x14ac:dyDescent="0.25"/>
+    <row r="578" x14ac:dyDescent="0.25"/>
+    <row r="579" x14ac:dyDescent="0.25"/>
+    <row r="580" x14ac:dyDescent="0.25"/>
+    <row r="581" x14ac:dyDescent="0.25"/>
+    <row r="582" x14ac:dyDescent="0.25"/>
+    <row r="583" x14ac:dyDescent="0.25"/>
+    <row r="584" x14ac:dyDescent="0.25"/>
+    <row r="585" x14ac:dyDescent="0.25"/>
+    <row r="586" x14ac:dyDescent="0.25"/>
+    <row r="587" x14ac:dyDescent="0.25"/>
+    <row r="588" x14ac:dyDescent="0.25"/>
+    <row r="589" x14ac:dyDescent="0.25"/>
+    <row r="590" x14ac:dyDescent="0.25"/>
+    <row r="591" x14ac:dyDescent="0.25"/>
+    <row r="592" x14ac:dyDescent="0.25"/>
+    <row r="593" x14ac:dyDescent="0.25"/>
+    <row r="594" x14ac:dyDescent="0.25"/>
+    <row r="595" x14ac:dyDescent="0.25"/>
+    <row r="596" x14ac:dyDescent="0.25"/>
+    <row r="597" x14ac:dyDescent="0.25"/>
+    <row r="598" x14ac:dyDescent="0.25"/>
+    <row r="599" x14ac:dyDescent="0.25"/>
+    <row r="600" x14ac:dyDescent="0.25"/>
+    <row r="601" x14ac:dyDescent="0.25"/>
+    <row r="602" x14ac:dyDescent="0.25"/>
+    <row r="603" x14ac:dyDescent="0.25"/>
+    <row r="604" x14ac:dyDescent="0.25"/>
+    <row r="605" x14ac:dyDescent="0.25"/>
+    <row r="606" x14ac:dyDescent="0.25"/>
+    <row r="607" x14ac:dyDescent="0.25"/>
+    <row r="608" x14ac:dyDescent="0.25"/>
+    <row r="609" x14ac:dyDescent="0.25"/>
+    <row r="610" x14ac:dyDescent="0.25"/>
+    <row r="611" x14ac:dyDescent="0.25"/>
+    <row r="612" x14ac:dyDescent="0.25"/>
+    <row r="613" x14ac:dyDescent="0.25"/>
+    <row r="614" x14ac:dyDescent="0.25"/>
+    <row r="615" x14ac:dyDescent="0.25"/>
+    <row r="616" x14ac:dyDescent="0.25"/>
+    <row r="617" x14ac:dyDescent="0.25"/>
+    <row r="618" x14ac:dyDescent="0.25"/>
+    <row r="619" x14ac:dyDescent="0.25"/>
+    <row r="620" x14ac:dyDescent="0.25"/>
+    <row r="621" x14ac:dyDescent="0.25"/>
+    <row r="622" x14ac:dyDescent="0.25"/>
+    <row r="623" x14ac:dyDescent="0.25"/>
+    <row r="624" x14ac:dyDescent="0.25"/>
+    <row r="625" x14ac:dyDescent="0.25"/>
+    <row r="626" x14ac:dyDescent="0.25"/>
+    <row r="627" x14ac:dyDescent="0.25"/>
+    <row r="628" x14ac:dyDescent="0.25"/>
+    <row r="629" x14ac:dyDescent="0.25"/>
+    <row r="630" x14ac:dyDescent="0.25"/>
+    <row r="631" x14ac:dyDescent="0.25"/>
+    <row r="632" x14ac:dyDescent="0.25"/>
+    <row r="633" x14ac:dyDescent="0.25"/>
+    <row r="634" x14ac:dyDescent="0.25"/>
+    <row r="635" x14ac:dyDescent="0.25"/>
+    <row r="636" x14ac:dyDescent="0.25"/>
+    <row r="637" x14ac:dyDescent="0.25"/>
+    <row r="638" x14ac:dyDescent="0.25"/>
+    <row r="639" x14ac:dyDescent="0.25"/>
+    <row r="640" x14ac:dyDescent="0.25"/>
+    <row r="641" x14ac:dyDescent="0.25"/>
+    <row r="642" x14ac:dyDescent="0.25"/>
+    <row r="643" x14ac:dyDescent="0.25"/>
+    <row r="644" x14ac:dyDescent="0.25"/>
+    <row r="645" x14ac:dyDescent="0.25"/>
+    <row r="646" x14ac:dyDescent="0.25"/>
+    <row r="647" x14ac:dyDescent="0.25"/>
+    <row r="648" x14ac:dyDescent="0.25"/>
+    <row r="649" x14ac:dyDescent="0.25"/>
+    <row r="650" x14ac:dyDescent="0.25"/>
+    <row r="651" x14ac:dyDescent="0.25"/>
+    <row r="652" x14ac:dyDescent="0.25"/>
+    <row r="653" x14ac:dyDescent="0.25"/>
+    <row r="654" x14ac:dyDescent="0.25"/>
+    <row r="655" x14ac:dyDescent="0.25"/>
+    <row r="656" x14ac:dyDescent="0.25"/>
+    <row r="657" x14ac:dyDescent="0.25"/>
+    <row r="658" x14ac:dyDescent="0.25"/>
+    <row r="659" x14ac:dyDescent="0.25"/>
+    <row r="660" x14ac:dyDescent="0.25"/>
+    <row r="661" x14ac:dyDescent="0.25"/>
+    <row r="662" x14ac:dyDescent="0.25"/>
+    <row r="663" x14ac:dyDescent="0.25"/>
+    <row r="664" x14ac:dyDescent="0.25"/>
+    <row r="665" x14ac:dyDescent="0.25"/>
+    <row r="666" x14ac:dyDescent="0.25"/>
+    <row r="667" x14ac:dyDescent="0.25"/>
+    <row r="668" x14ac:dyDescent="0.25"/>
+    <row r="669" x14ac:dyDescent="0.25"/>
+    <row r="670" x14ac:dyDescent="0.25"/>
+    <row r="671" x14ac:dyDescent="0.25"/>
+    <row r="672" x14ac:dyDescent="0.25"/>
+    <row r="673" x14ac:dyDescent="0.25"/>
+    <row r="674" x14ac:dyDescent="0.25"/>
+    <row r="675" x14ac:dyDescent="0.25"/>
+    <row r="676" x14ac:dyDescent="0.25"/>
+    <row r="677" x14ac:dyDescent="0.25"/>
+    <row r="678" x14ac:dyDescent="0.25"/>
+    <row r="679" x14ac:dyDescent="0.25"/>
+    <row r="680" x14ac:dyDescent="0.25"/>
+    <row r="681" x14ac:dyDescent="0.25"/>
+    <row r="682" x14ac:dyDescent="0.25"/>
+    <row r="683" x14ac:dyDescent="0.25"/>
+    <row r="684" x14ac:dyDescent="0.25"/>
+    <row r="685" x14ac:dyDescent="0.25"/>
+    <row r="686" x14ac:dyDescent="0.25"/>
+    <row r="687" x14ac:dyDescent="0.25"/>
+    <row r="688" x14ac:dyDescent="0.25"/>
+    <row r="689" x14ac:dyDescent="0.25"/>
+    <row r="690" x14ac:dyDescent="0.25"/>
+    <row r="691" x14ac:dyDescent="0.25"/>
+    <row r="692" x14ac:dyDescent="0.25"/>
+    <row r="693" x14ac:dyDescent="0.25"/>
+    <row r="694" x14ac:dyDescent="0.25"/>
+    <row r="695" x14ac:dyDescent="0.25"/>
+    <row r="696" x14ac:dyDescent="0.25"/>
+    <row r="697" x14ac:dyDescent="0.25"/>
+    <row r="698" x14ac:dyDescent="0.25"/>
+    <row r="699" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="C142:C1048576 C1:C140">
-    <cfRule type="containsText" dxfId="20" priority="36" operator="containsText" text="CC">
+  <conditionalFormatting sqref="C1:C140 C142:C1048576">
+    <cfRule type="containsText" dxfId="9" priority="36" operator="containsText" text="CC">
       <formula>NOT(ISERROR(SEARCH("CC",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C696">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*TIP*">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*TIP*">
       <formula>NOT(ISERROR(SEARCH("*TIP*",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I696">
-    <cfRule type="containsText" dxfId="18" priority="38" operator="containsText" text="Unpaid">
+    <cfRule type="containsText" dxfId="7" priority="38" operator="containsText" text="Unpaid">
       <formula>NOT(ISERROR(SEARCH("Unpaid",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="39" operator="containsText" text="paid">
+    <cfRule type="containsText" dxfId="6" priority="39" operator="containsText" text="paid">
       <formula>NOT(ISERROR(SEARCH("paid",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9549,10 +9549,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9804,7 +9804,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:T86"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
@@ -9826,7 +9826,7 @@
     <col min="20" max="20" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -9848,59 +9848,59 @@
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
     </row>
-    <row r="2" spans="1:20" ht="21.75" customHeight="1">
+    <row r="2" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
       <c r="F2" s="13"/>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="86"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:20" ht="18.75" customHeight="1">
+    <row r="3" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="35" t="s">
         <v>14</v>
@@ -9956,9 +9956,9 @@
       </c>
       <c r="T4" s="12"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
-      <c r="B5" s="74" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="2">
@@ -10019,15 +10019,15 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B5)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="77">
+      <c r="S5" s="73">
         <f>SUM(G5:R5)</f>
         <v>8133.0599999999995</v>
       </c>
       <c r="T5" s="12"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="74" t="s">
+      <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" s="2">
@@ -10088,15 +10088,15 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B6)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="77">
+      <c r="S6" s="73">
         <f t="shared" ref="S6:S11" si="0">SUM(G6:R6)</f>
         <v>5733.7999999999993</v>
       </c>
       <c r="T6" s="12"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="74" t="s">
+      <c r="B7" t="s">
         <v>93</v>
       </c>
       <c r="C7" s="2">
@@ -10157,15 +10157,15 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B7)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="73">
         <f t="shared" si="0"/>
         <v>7203.2300000000005</v>
       </c>
       <c r="T7" s="12"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="74" t="s">
+      <c r="B8" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2">
@@ -10226,12 +10226,12 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B8)</f>
         <v>0</v>
       </c>
-      <c r="S8" s="77"/>
+      <c r="S8" s="73"/>
       <c r="T8" s="12"/>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="74" t="s">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="2">
@@ -10292,13 +10292,13 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B9)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="77">
+      <c r="S9" s="73">
         <f t="shared" ref="S9" si="1">SUM(G9:R9)</f>
         <v>486.89</v>
       </c>
       <c r="T9" s="12"/>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="31"/>
       <c r="C10" s="2">
@@ -10359,13 +10359,13 @@
         <f>SUMIFS(Logbook!$E$1:$E$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$C$1:$C$696,DashBoard!$B10)</f>
         <v>0</v>
       </c>
-      <c r="S10" s="77">
+      <c r="S10" s="73">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T10" s="12"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="35" t="s">
         <v>158</v>
@@ -10383,72 +10383,72 @@
         <v>3944.27</v>
       </c>
       <c r="F11" s="36"/>
-      <c r="G11" s="77">
+      <c r="G11" s="73">
         <f t="shared" ref="G11:R11" si="3">SUM(G5:G10)</f>
         <v>17472.919999999998</v>
       </c>
-      <c r="H11" s="77">
+      <c r="H11" s="73">
         <f t="shared" si="3"/>
         <v>4084.27</v>
       </c>
-      <c r="I11" s="77">
+      <c r="I11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="77">
+      <c r="J11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="77">
+      <c r="K11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="77">
+      <c r="L11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M11" s="77">
+      <c r="M11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N11" s="77">
+      <c r="N11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O11" s="77">
+      <c r="O11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P11" s="77">
+      <c r="P11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="77">
+      <c r="Q11" s="73">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="78">
+      <c r="R11" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S11" s="77">
+      <c r="S11" s="73">
         <f t="shared" si="0"/>
         <v>21557.19</v>
       </c>
       <c r="T11" s="12"/>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="69" t="s">
         <v>146</v>
       </c>
       <c r="F12" s="12"/>
@@ -10463,11 +10463,11 @@
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="73"/>
+      <c r="R12" s="72"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="35" t="s">
         <v>159</v>
@@ -10523,9 +10523,9 @@
       </c>
       <c r="T13" s="12"/>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="74" t="s">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="32">
@@ -10587,15 +10587,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B14)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="79">
+      <c r="S14" s="75">
         <f>SUM(G14:R14)</f>
         <v>2100</v>
       </c>
       <c r="T14" s="12"/>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="74" t="s">
+      <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="32">
@@ -10657,15 +10657,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B15)</f>
         <v>0</v>
       </c>
-      <c r="S15" s="83">
-        <f t="shared" ref="S15:S31" si="5">SUM(G15:R15)</f>
+      <c r="S15" s="79">
+        <f t="shared" ref="S15:S28" si="5">SUM(G15:R15)</f>
         <v>2100</v>
       </c>
       <c r="T15" s="12"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="74" t="s">
+      <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="32">
@@ -10727,15 +10727,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B16)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="83">
+      <c r="S16" s="79">
         <f t="shared" si="5"/>
         <v>614</v>
       </c>
       <c r="T16" s="12"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="74" t="s">
+      <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="32">
@@ -10797,15 +10797,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B17)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="79">
+      <c r="S17" s="75">
         <f t="shared" si="5"/>
         <v>5471.44</v>
       </c>
       <c r="T17" s="4"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="74" t="s">
+      <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="32">
@@ -10867,15 +10867,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B18)</f>
         <v>0</v>
       </c>
-      <c r="S18" s="79">
+      <c r="S18" s="75">
         <f t="shared" si="5"/>
         <v>1510.5800000000002</v>
       </c>
       <c r="T18" s="4"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="74" t="s">
+      <c r="B19" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="32">
@@ -10937,15 +10937,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B19)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="79">
+      <c r="S19" s="75">
         <f t="shared" si="5"/>
         <v>633.25</v>
       </c>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="74" t="s">
+      <c r="B20" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="32">
@@ -11007,15 +11007,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B20)</f>
         <v>0</v>
       </c>
-      <c r="S20" s="79">
+      <c r="S20" s="75">
         <f t="shared" si="5"/>
         <v>637.63000000000011</v>
       </c>
       <c r="T20" s="4"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="74" t="s">
+      <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="32">
@@ -11077,15 +11077,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B21)</f>
         <v>0</v>
       </c>
-      <c r="S21" s="79">
+      <c r="S21" s="75">
         <f t="shared" ref="S21" si="7">SUM(G21:R21)</f>
         <v>1697.3</v>
       </c>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="74" t="s">
+      <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="32">
@@ -11147,15 +11147,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B22)</f>
         <v>0</v>
       </c>
-      <c r="S22" s="79">
+      <c r="S22" s="75">
         <f t="shared" si="5"/>
         <v>1081.9299999999998</v>
       </c>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="74" t="s">
+      <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="32">
@@ -11217,15 +11217,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B23)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="79">
+      <c r="S23" s="75">
         <f t="shared" si="5"/>
         <v>435.59</v>
       </c>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="74" t="s">
+      <c r="B24" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="32">
@@ -11287,15 +11287,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B24)</f>
         <v>0</v>
       </c>
-      <c r="S24" s="79">
+      <c r="S24" s="75">
         <f t="shared" si="5"/>
         <v>625.59999999999991</v>
       </c>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-      <c r="B25" s="74" t="s">
+      <c r="B25" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="32">
@@ -11357,15 +11357,15 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B25)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="79">
+      <c r="S25" s="75">
         <f t="shared" si="5"/>
         <v>385.6</v>
       </c>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="74" t="s">
+      <c r="B26" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="2">
@@ -11425,13 +11425,13 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B26)</f>
         <v>0</v>
       </c>
-      <c r="S26" s="83">
+      <c r="S26" s="79">
         <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="T26" s="4"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="31"/>
       <c r="C27" s="2">
@@ -11491,13 +11491,13 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B27)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="76">
+      <c r="S27" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T27" s="4"/>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="31"/>
       <c r="C28" s="2">
@@ -11557,13 +11557,13 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B28)</f>
         <v>0</v>
       </c>
-      <c r="S28" s="76">
+      <c r="S28" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T28" s="4"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="31"/>
       <c r="C29" s="2">
@@ -11623,13 +11623,13 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B29)</f>
         <v>0</v>
       </c>
-      <c r="S29" s="76">
+      <c r="S29" s="38">
         <f t="shared" ref="S29" si="9">SUM(G29:R29)</f>
         <v>0</v>
       </c>
       <c r="T29" s="4"/>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="31"/>
       <c r="C30" s="2">
@@ -11689,413 +11689,387 @@
         <f>SUMIFS(Logbook!$F$1:$F$696,Logbook!$A$1:$A$696,DashBoard!R$4,Logbook!$D$1:$D$696,DashBoard!$B30)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="76">
+      <c r="S30" s="38">
         <f t="shared" ref="S30" si="11">SUM(G30:R30)</f>
         <v>0</v>
       </c>
       <c r="T30" s="4"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="75">
+      <c r="C31" s="36">
         <f>SUM(C14:C27)</f>
         <v>13018.039999999997</v>
       </c>
-      <c r="D31" s="75">
+      <c r="D31" s="36">
         <f>SUM(D14:D30)</f>
         <v>10500</v>
       </c>
-      <c r="E31" s="76">
+      <c r="E31" s="38">
         <f>SUM(E14,E17,E18,E19,E20,E21,E22,E23,E24,E25,E27,E28,E29,E30,E15,E16)</f>
         <v>3481.9600000000005</v>
       </c>
       <c r="F31" s="40">
-        <f>SUM(F14,F17,F18,F19,F20,F21,F22,F23,F24,F25,F27,F28,F29,F30)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="79">
-        <f>SUM(G14,G17,G18,G19,G20,G21,G22,G23,G24,G25,G27,G28,G29,G30)</f>
+        <f t="shared" ref="F31:S31" si="12">SUM(F14,F17,F18,F19,F20,F21,F22,F23,F24,F25,F27,F28,F29,F30)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="12"/>
         <v>7560.8799999999992</v>
       </c>
-      <c r="H31" s="79">
-        <f>SUM(H14,H17,H18,H19,H20,H21,H22,H23,H24,H25,H27,H28,H29,H30)</f>
+      <c r="H31" s="75">
+        <f t="shared" si="12"/>
         <v>7018.0399999999981</v>
       </c>
-      <c r="I31" s="79">
-        <f>SUM(I14,I17,I18,I19,I20,I21,I22,I23,I24,I25,I27,I28,I29,I30)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="79">
-        <f>SUM(J14,J17,J18,J19,J20,J21,J22,J23,J24,J25,J27,J28,J29,J30)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="79">
-        <f>SUM(K14,K17,K18,K19,K20,K21,K22,K23,K24,K25,K27,K28,K29,K30)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="79">
-        <f>SUM(L14,L17,L18,L19,L20,L21,L22,L23,L24,L25,L27,L28,L29,L30)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="79">
-        <f>SUM(M14,M17,M18,M19,M20,M21,M22,M23,M24,M25,M27,M28,M29,M30)</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="79">
-        <f>SUM(N14,N17,N18,N19,N20,N21,N22,N23,N24,N25,N27,N28,N29,N30)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="79">
-        <f>SUM(O14,O17,O18,O19,O20,O21,O22,O23,O24,O25,O27,O28,O29,O30)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="79">
-        <f>SUM(P14,P17,P18,P19,P20,P21,P22,P23,P24,P25,P27,P28,P29,P30)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="79">
-        <f>SUM(Q14,Q17,Q18,Q19,Q20,Q21,Q22,Q23,Q24,Q25,Q27,Q28,Q29,Q30)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="79">
-        <f>SUM(R14,R17,R18,R19,R20,R21,R22,R23,R24,R25,R27,R28,R29,R30)</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="79">
-        <f>SUM(S14,S17,S18,S19,S20,S21,S22,S23,S24,S25,S27,S28,S29,S30)</f>
+      <c r="I31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="75">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="75">
+        <f t="shared" si="12"/>
         <v>14578.920000000002</v>
       </c>
       <c r="T31" s="4"/>
     </row>
-    <row r="32" spans="1:20" ht="14.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="32" spans="1:20" ht="14.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="74"/>
       <c r="T32" s="4"/>
     </row>
-    <row r="33" spans="1:20" ht="14.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="33" spans="1:20" ht="14.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="74"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="74"/>
-      <c r="S33" s="74"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="1:20" collapsed="1">
+    <row r="34" spans="1:20" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="72"/>
-      <c r="G34" s="80">
-        <f t="shared" ref="G34:S34" si="12">G11-G31</f>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="71"/>
+      <c r="G34" s="76">
+        <f t="shared" ref="G34:S34" si="13">G11-G31</f>
         <v>9912.0399999999991</v>
       </c>
-      <c r="H34" s="80">
-        <f t="shared" si="12"/>
+      <c r="H34" s="76">
+        <f t="shared" si="13"/>
         <v>-2933.7699999999982</v>
       </c>
-      <c r="I34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="80">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="80">
-        <f t="shared" si="12"/>
+      <c r="I34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="76">
+        <f t="shared" si="13"/>
         <v>6978.2699999999968</v>
       </c>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="82"/>
-      <c r="N35" s="82"/>
-      <c r="O35" s="82"/>
-      <c r="P35" s="82"/>
-      <c r="Q35" s="82"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="83">
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="78"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="78"/>
+      <c r="M35" s="78"/>
+      <c r="N35" s="78"/>
+      <c r="O35" s="78"/>
+      <c r="P35" s="78"/>
+      <c r="Q35" s="78"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="79">
         <f>SUM(S15,S16,S26)</f>
         <v>8714</v>
       </c>
       <c r="T35" s="4"/>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="T36" s="4"/>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="T37" s="4"/>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="T39" s="4"/>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="T41" s="4"/>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="T42" s="4"/>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="T43" s="4"/>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="T44" s="4"/>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="T45" s="4"/>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="T46" s="4"/>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="T47" s="4"/>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="T48" s="4"/>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="T49" s="4"/>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="T50" s="4"/>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="T51" s="4"/>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="T52" s="4"/>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="T53" s="4"/>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="T54" s="4"/>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="T55" s="4"/>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="T56" s="4"/>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="T57" s="4"/>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="T58" s="4"/>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="T59" s="4"/>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="T60" s="4"/>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="T61" s="4"/>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="T62" s="4"/>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="T63" s="4"/>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="T64" s="4"/>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="T65" s="4"/>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="T66" s="4"/>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="T67" s="4"/>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="T68" s="4"/>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="T69" s="4"/>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="T70" s="4"/>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="T71" s="4"/>
     </row>
-    <row r="72" spans="1:20">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="T72" s="4"/>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="T73" s="4"/>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="T74" s="4"/>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="T75" s="4"/>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="T76" s="4"/>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="T77" s="4"/>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="T78" s="4"/>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="T79" s="4"/>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="T80" s="4"/>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="T81" s="4"/>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="T82" s="4"/>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="T83" s="4"/>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="T84" s="4"/>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="T85" s="4"/>
     </row>
-    <row r="86" spans="1:20">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -12125,10 +12099,10 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E14:E30">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12163,10 +12137,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:S34">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12187,7 +12161,7 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:E89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -12195,7 +12169,7 @@
     <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="57" t="s">
         <v>161</v>
       </c>
@@ -12212,11 +12186,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="69">
+      <c r="B2" s="68">
         <v>46046</v>
       </c>
       <c r="C2" s="56" t="s">
@@ -12229,649 +12203,649 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="61" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
         <v>166</v>
       </c>
       <c r="B3" s="42">
         <v>46054</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="62" t="s">
         <v>168</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
         <v>170</v>
       </c>
       <c r="B4" s="42">
         <v>46059</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>171</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
         <v>170</v>
       </c>
       <c r="B5" s="42">
         <v>46063</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="62" t="s">
         <v>171</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="64">
         <v>46067</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>171</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44"/>
       <c r="B7" s="45"/>
-      <c r="C7" s="67"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="63"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="62"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="67"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="43"/>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="63"/>
+      <c r="E8" s="62"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="62"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="67"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="43"/>
-      <c r="E9" s="63"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="63"/>
+      <c r="E9" s="62"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="62"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="67"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="43"/>
-      <c r="E10" s="63"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="61"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="61"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E10" s="62"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="60"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="60"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="49"/>
-      <c r="B12" s="68"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="51"/>
       <c r="D12" s="52"/>
       <c r="E12" s="49"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="47"/>
       <c r="B13" s="45"/>
       <c r="C13" s="48"/>
       <c r="D13" s="46"/>
       <c r="E13" s="55"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="47"/>
       <c r="B14" s="45"/>
       <c r="C14" s="48"/>
       <c r="D14" s="46"/>
       <c r="E14" s="55"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="47"/>
       <c r="B15" s="45"/>
       <c r="C15" s="48"/>
       <c r="D15" s="46"/>
       <c r="E15" s="55"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="47"/>
       <c r="B16" s="45"/>
       <c r="C16" s="48"/>
       <c r="D16" s="46"/>
       <c r="E16" s="55"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="47"/>
       <c r="B17" s="45"/>
       <c r="C17" s="48"/>
       <c r="D17" s="46"/>
       <c r="E17" s="55"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47"/>
       <c r="B18" s="45"/>
       <c r="C18" s="48"/>
       <c r="D18" s="46"/>
       <c r="E18" s="55"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="47"/>
       <c r="C19" s="48"/>
       <c r="D19" s="46"/>
       <c r="E19" s="44"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
       <c r="B20" s="47"/>
       <c r="C20" s="48"/>
       <c r="D20" s="46"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
       <c r="B21" s="47"/>
       <c r="C21" s="48"/>
       <c r="D21" s="46"/>
       <c r="E21" s="44"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="47"/>
       <c r="C22" s="48"/>
       <c r="D22" s="46"/>
       <c r="E22" s="44"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
       <c r="B23" s="47"/>
       <c r="C23" s="48"/>
       <c r="D23" s="46"/>
       <c r="E23" s="44"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
       <c r="B24" s="47"/>
       <c r="C24" s="48"/>
       <c r="D24" s="46"/>
       <c r="E24" s="44"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
       <c r="B25" s="47"/>
       <c r="C25" s="48"/>
       <c r="D25" s="46"/>
       <c r="E25" s="44"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
       <c r="B26" s="47"/>
       <c r="C26" s="48"/>
       <c r="D26" s="46"/>
       <c r="E26" s="44"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
       <c r="B27" s="47"/>
       <c r="C27" s="48"/>
       <c r="D27" s="46"/>
       <c r="E27" s="44"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
       <c r="B28" s="47"/>
       <c r="C28" s="48"/>
       <c r="D28" s="46"/>
       <c r="E28" s="44"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
       <c r="B29" s="47"/>
       <c r="C29" s="48"/>
       <c r="D29" s="46"/>
       <c r="E29" s="44"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
       <c r="B30" s="47"/>
       <c r="C30" s="48"/>
       <c r="D30" s="46"/>
       <c r="E30" s="44"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
       <c r="B31" s="47"/>
       <c r="C31" s="48"/>
       <c r="D31" s="46"/>
       <c r="E31" s="44"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
       <c r="B32" s="47"/>
       <c r="C32" s="48"/>
       <c r="D32" s="46"/>
       <c r="E32" s="44"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
       <c r="B33" s="47"/>
       <c r="C33" s="48"/>
       <c r="D33" s="46"/>
       <c r="E33" s="44"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
       <c r="B34" s="47"/>
       <c r="C34" s="48"/>
       <c r="D34" s="46"/>
       <c r="E34" s="44"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
       <c r="B35" s="47"/>
       <c r="C35" s="48"/>
       <c r="D35" s="46"/>
       <c r="E35" s="44"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="44"/>
       <c r="B36" s="47"/>
       <c r="C36" s="48"/>
       <c r="D36" s="46"/>
       <c r="E36" s="44"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="44"/>
       <c r="B37" s="47"/>
       <c r="C37" s="48"/>
       <c r="D37" s="46"/>
       <c r="E37" s="44"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
       <c r="B38" s="47"/>
       <c r="C38" s="48"/>
       <c r="D38" s="46"/>
       <c r="E38" s="44"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="44"/>
       <c r="B39" s="47"/>
       <c r="C39" s="48"/>
       <c r="D39" s="46"/>
       <c r="E39" s="44"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
       <c r="B40" s="47"/>
       <c r="C40" s="48"/>
       <c r="D40" s="46"/>
       <c r="E40" s="44"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
       <c r="B41" s="47"/>
       <c r="C41" s="48"/>
       <c r="D41" s="46"/>
       <c r="E41" s="44"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="44"/>
       <c r="B42" s="47"/>
       <c r="C42" s="48"/>
       <c r="D42" s="46"/>
       <c r="E42" s="44"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
       <c r="B43" s="47"/>
       <c r="C43" s="48"/>
       <c r="D43" s="46"/>
       <c r="E43" s="44"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="44"/>
       <c r="B44" s="47"/>
       <c r="C44" s="48"/>
       <c r="D44" s="46"/>
       <c r="E44" s="44"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
       <c r="B45" s="47"/>
       <c r="C45" s="48"/>
       <c r="D45" s="46"/>
       <c r="E45" s="44"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
       <c r="B46" s="47"/>
       <c r="C46" s="48"/>
       <c r="D46" s="46"/>
       <c r="E46" s="44"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
       <c r="B47" s="47"/>
       <c r="C47" s="48"/>
       <c r="D47" s="46"/>
       <c r="E47" s="44"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
       <c r="B48" s="47"/>
       <c r="C48" s="48"/>
       <c r="D48" s="46"/>
       <c r="E48" s="44"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
       <c r="B49" s="47"/>
       <c r="C49" s="48"/>
       <c r="D49" s="46"/>
       <c r="E49" s="44"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="47"/>
       <c r="C50" s="48"/>
       <c r="D50" s="46"/>
       <c r="E50" s="44"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="44"/>
       <c r="B51" s="47"/>
       <c r="C51" s="48"/>
       <c r="D51" s="46"/>
       <c r="E51" s="44"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="44"/>
       <c r="B52" s="47"/>
       <c r="C52" s="48"/>
       <c r="D52" s="46"/>
       <c r="E52" s="44"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="44"/>
       <c r="B53" s="47"/>
       <c r="C53" s="48"/>
       <c r="D53" s="46"/>
       <c r="E53" s="44"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="44"/>
       <c r="B54" s="47"/>
       <c r="C54" s="48"/>
       <c r="D54" s="46"/>
       <c r="E54" s="44"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="44"/>
       <c r="B55" s="47"/>
       <c r="C55" s="48"/>
       <c r="D55" s="46"/>
       <c r="E55" s="44"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="44"/>
       <c r="B56" s="47"/>
       <c r="C56" s="48"/>
       <c r="D56" s="46"/>
       <c r="E56" s="44"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
       <c r="B57" s="47"/>
       <c r="C57" s="48"/>
       <c r="D57" s="46"/>
       <c r="E57" s="44"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="44"/>
       <c r="B58" s="47"/>
       <c r="C58" s="48"/>
       <c r="D58" s="46"/>
       <c r="E58" s="44"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="44"/>
       <c r="B59" s="47"/>
       <c r="C59" s="48"/>
       <c r="D59" s="46"/>
       <c r="E59" s="44"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="44"/>
       <c r="B60" s="47"/>
       <c r="C60" s="48"/>
       <c r="D60" s="46"/>
       <c r="E60" s="44"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="44"/>
       <c r="B61" s="47"/>
       <c r="C61" s="48"/>
       <c r="D61" s="46"/>
       <c r="E61" s="44"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="44"/>
       <c r="B62" s="47"/>
       <c r="C62" s="48"/>
       <c r="D62" s="46"/>
       <c r="E62" s="44"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="44"/>
       <c r="B63" s="47"/>
       <c r="C63" s="48"/>
       <c r="D63" s="46"/>
       <c r="E63" s="44"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="44"/>
       <c r="B64" s="47"/>
       <c r="C64" s="48"/>
       <c r="D64" s="46"/>
       <c r="E64" s="44"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="44"/>
       <c r="B65" s="47"/>
       <c r="C65" s="48"/>
       <c r="D65" s="46"/>
       <c r="E65" s="44"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="44"/>
       <c r="B66" s="47"/>
       <c r="C66" s="48"/>
       <c r="D66" s="46"/>
       <c r="E66" s="44"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="44"/>
       <c r="B67" s="47"/>
       <c r="C67" s="48"/>
       <c r="D67" s="46"/>
       <c r="E67" s="44"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="44"/>
       <c r="B68" s="47"/>
       <c r="C68" s="48"/>
       <c r="D68" s="46"/>
       <c r="E68" s="44"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="44"/>
       <c r="B69" s="47"/>
       <c r="C69" s="48"/>
       <c r="D69" s="46"/>
       <c r="E69" s="44"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="44"/>
       <c r="B70" s="47"/>
       <c r="C70" s="48"/>
       <c r="D70" s="46"/>
       <c r="E70" s="44"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="44"/>
       <c r="B71" s="47"/>
       <c r="C71" s="48"/>
       <c r="D71" s="46"/>
       <c r="E71" s="44"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="44"/>
       <c r="B72" s="47"/>
       <c r="C72" s="48"/>
       <c r="D72" s="46"/>
       <c r="E72" s="44"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="44"/>
       <c r="B73" s="47"/>
       <c r="C73" s="48"/>
       <c r="D73" s="46"/>
       <c r="E73" s="44"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="44"/>
       <c r="B74" s="47"/>
       <c r="C74" s="48"/>
       <c r="D74" s="46"/>
       <c r="E74" s="44"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="44"/>
       <c r="B75" s="47"/>
       <c r="C75" s="48"/>
       <c r="D75" s="46"/>
       <c r="E75" s="44"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="44"/>
       <c r="B76" s="47"/>
       <c r="C76" s="48"/>
       <c r="D76" s="46"/>
       <c r="E76" s="44"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="44"/>
       <c r="B77" s="47"/>
       <c r="C77" s="48"/>
       <c r="D77" s="46"/>
       <c r="E77" s="44"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="44"/>
       <c r="B78" s="47"/>
       <c r="C78" s="48"/>
       <c r="D78" s="46"/>
       <c r="E78" s="44"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="44"/>
       <c r="B79" s="47"/>
       <c r="C79" s="48"/>
       <c r="D79" s="46"/>
       <c r="E79" s="44"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="44"/>
       <c r="B80" s="47"/>
       <c r="C80" s="48"/>
       <c r="D80" s="46"/>
       <c r="E80" s="44"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="44"/>
       <c r="B81" s="47"/>
       <c r="C81" s="48"/>
       <c r="D81" s="46"/>
       <c r="E81" s="44"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="44"/>
       <c r="B82" s="47"/>
       <c r="C82" s="48"/>
       <c r="D82" s="46"/>
       <c r="E82" s="44"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="44"/>
       <c r="B83" s="47"/>
       <c r="C83" s="48"/>
       <c r="D83" s="46"/>
       <c r="E83" s="44"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="44"/>
       <c r="B84" s="47"/>
       <c r="C84" s="48"/>
       <c r="D84" s="46"/>
       <c r="E84" s="44"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="44"/>
       <c r="B85" s="47"/>
       <c r="C85" s="48"/>
       <c r="D85" s="46"/>
       <c r="E85" s="44"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="44"/>
       <c r="B86" s="47"/>
       <c r="C86" s="48"/>
       <c r="D86" s="46"/>
       <c r="E86" s="44"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="44"/>
       <c r="B87" s="47"/>
       <c r="C87" s="48"/>
       <c r="D87" s="46"/>
       <c r="E87" s="44"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="44"/>
       <c r="B88" s="47"/>
       <c r="C88" s="48"/>
       <c r="D88" s="46"/>
       <c r="E88" s="44"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="49"/>
       <c r="B89" s="50"/>
       <c r="C89" s="51"/>
